--- a/order_forms/033_purchase_order_data_upload_form--order_forms.xlsx
+++ b/order_forms/033_purchase_order_data_upload_form--order_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vendor_name</t>
+          <t>vendor_name_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vendor Name</t>
+          <t>Vendor Name 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>order_number</t>
+          <t>order_number_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Order Number</t>
+          <t>Order Number 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vendor_address</t>
+          <t>vendor_address_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vendor Address</t>
+          <t>Vendor Address 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>supporting_documents</t>
+          <t>supporting_documents_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Supporting Documents</t>
+          <t>Supporting Documents 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>delivery_date</t>
+          <t>delivery_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
+          <t>Delivery Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>delivery_time</t>
+          <t>delivery_time_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
+          <t>Delivery Time 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>purchase_order_data</t>
+          <t>purchase_order_data_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Purchase Order Data</t>
+          <t>Purchase Order Data 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>order_details</t>
+          <t>order_details_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Order Details</t>
+          <t>Order Details 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>delivery_information</t>
+          <t>delivery_information_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Delivery Information</t>
+          <t>Delivery Information 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
